--- a/src/generated_files/mappings.xlsx
+++ b/src/generated_files/mappings.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="121">
   <si>
     <t>FFMPEG Generic Tag Name</t>
   </si>
@@ -334,10 +334,10 @@
     <t>the total bitrate of the bitrate variant that the current stream is part of</t>
   </si>
   <si>
-    <t>MEDIA</t>
-  </si>
-  <si>
-    <t>source media of audio</t>
+    <t>as found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source media of audio, as found, eg: MEDIA | media_type </t>
   </si>
   <si>
     <t>TMED</t>
@@ -352,10 +352,10 @@
     <t>maybe</t>
   </si>
   <si>
-    <t>COMPILATION</t>
-  </si>
-  <si>
-    <t>is a compilation</t>
+    <t/>
+  </si>
+  <si>
+    <t xml:space="preserve">is a compilation, as found </t>
   </si>
   <si>
     <t>TCMP</t>
@@ -365,6 +365,9 @@
   </si>
   <si>
     <t>WM/IsCompilation</t>
+  </si>
+  <si>
+    <t>cover art</t>
   </si>
   <si>
     <t>APIC</t>
@@ -381,7 +384,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -399,12 +402,6 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -455,7 +452,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -472,8 +469,11 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -789,16 +789,16 @@
   <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="8" width="25.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="66.57642857142856" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="9" width="16.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="8" width="21.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="8" width="27.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="27.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="9" width="25.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="9" width="66.57642857142856" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="10" width="16.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="9" width="21.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="9" width="27.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="9" width="27.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -821,7 +821,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -844,7 +844,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
@@ -867,7 +867,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
@@ -890,7 +890,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3" t="s">
         <v>26</v>
       </c>
@@ -913,7 +913,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3" t="s">
         <v>32</v>
       </c>
@@ -936,7 +936,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3" t="s">
         <v>38</v>
       </c>
@@ -959,7 +959,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1" t="s">
         <v>43</v>
       </c>
@@ -982,7 +982,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3" t="s">
         <v>48</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
         <v>53</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="1" t="s">
         <v>59</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="1" t="s">
         <v>62</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="1" t="s">
         <v>68</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3" t="s">
         <v>70</v>
       </c>
@@ -1120,7 +1120,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="1" t="s">
         <v>76</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="1" t="s">
         <v>79</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3" t="s">
         <v>83</v>
       </c>
@@ -1189,7 +1189,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="1" t="s">
         <v>89</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="1" t="s">
         <v>91</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="3" t="s">
         <v>93</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="3" t="s">
         <v>98</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="1" t="s">
         <v>104</v>
       </c>
@@ -1304,7 +1304,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="1" t="s">
         <v>106</v>
       </c>
@@ -1327,14 +1327,14 @@
         <v>111</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
-      <c r="A24" s="1" t="s">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="6" t="s">
         <v>112</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D24" s="1" t="s">
@@ -1351,48 +1351,54 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="6" t="s">
+      <c r="A25" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E25" s="7" t="s">
+      <c r="D25" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="E25" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="G25" s="7"/>
+      <c r="F25" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
       <c r="C28" s="1"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/generated_files/mappings.xlsx
+++ b/src/generated_files/mappings.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="120">
   <si>
     <t>FFMPEG Generic Tag Name</t>
   </si>
@@ -346,13 +346,10 @@
     <t>----:com.apple.iTunes:MEDIA</t>
   </si>
   <si>
-    <t>WM/Media</t>
+    <t>WM/Media | media_type</t>
   </si>
   <si>
     <t>maybe</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t xml:space="preserve">is a compilation, as found </t>
@@ -452,7 +449,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -468,12 +465,6 @@
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -789,13 +780,13 @@
   <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="9" width="25.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="9" width="66.57642857142856" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="10" width="16.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="9" width="21.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="9" width="27.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="27.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="7" width="25.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="41.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="16.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="21.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="7" width="27.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="7" width="27.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -1328,77 +1319,77 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="F24" s="5" t="s">
         <v>115</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>116</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>117</v>
+      <c r="A25" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>116</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="F25" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="F25" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
       <c r="C26" s="1"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
       <c r="C27" s="1"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
       <c r="C28" s="1"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/generated_files/mappings.xlsx
+++ b/src/generated_files/mappings.xlsx
@@ -49,7 +49,7 @@
     <t>TALB</t>
   </si>
   <si>
-    <t xml:space="preserve"> @alb</t>
+    <t xml:space="preserve"> ©alb</t>
   </si>
   <si>
     <t>WM/AlbumTitle</t>
@@ -88,7 +88,7 @@
     <t>TPE1</t>
   </si>
   <si>
-    <t xml:space="preserve"> @art | @ART</t>
+    <t xml:space="preserve"> ©art | ©ART</t>
   </si>
   <si>
     <t>Author</t>
@@ -106,7 +106,7 @@
     <t>COMM:description</t>
   </si>
   <si>
-    <t xml:space="preserve"> @cmt</t>
+    <t xml:space="preserve"> ©cmt</t>
   </si>
   <si>
     <t>Description | WM/Comments</t>
@@ -124,7 +124,7 @@
     <t>TCOM</t>
   </si>
   <si>
-    <t xml:space="preserve"> @wrt</t>
+    <t xml:space="preserve"> ©wrt</t>
   </si>
   <si>
     <t>WM/Composer</t>
@@ -169,7 +169,7 @@
     <t>TYER</t>
   </si>
   <si>
-    <t xml:space="preserve"> @day</t>
+    <t xml:space="preserve"> ©day</t>
   </si>
   <si>
     <t>WM/Year</t>
@@ -214,7 +214,7 @@
     <t>TENC</t>
   </si>
   <si>
-    <t xml:space="preserve"> @enc | ©too</t>
+    <t xml:space="preserve"> ©enc | ©too</t>
   </si>
   <si>
     <t>WM/EncodedBy</t>
@@ -238,7 +238,7 @@
     <t>TCON</t>
   </si>
   <si>
-    <t xml:space="preserve"> @gen | gnre</t>
+    <t xml:space="preserve"> ©gen | gnre</t>
   </si>
   <si>
     <t>WM/Genre</t>
@@ -277,7 +277,7 @@
     <t>TPUB</t>
   </si>
   <si>
-    <t xml:space="preserve"> @pub</t>
+    <t xml:space="preserve"> ©pub</t>
   </si>
   <si>
     <t>WM/Publisher</t>
@@ -307,7 +307,7 @@
     <t>TIT2</t>
   </si>
   <si>
-    <t xml:space="preserve"> @nam</t>
+    <t xml:space="preserve"> ©nam</t>
   </si>
   <si>
     <t>track</t>
@@ -789,7 +789,7 @@
     <col min="7" max="7" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -812,7 +812,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -835,7 +835,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
@@ -858,7 +858,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
@@ -881,7 +881,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3" t="s">
         <v>26</v>
       </c>
@@ -904,7 +904,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3" t="s">
         <v>32</v>
       </c>
@@ -927,7 +927,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3" t="s">
         <v>38</v>
       </c>
@@ -950,7 +950,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1" t="s">
         <v>43</v>
       </c>
@@ -973,7 +973,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="3" t="s">
         <v>48</v>
       </c>
@@ -996,7 +996,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3" t="s">
         <v>53</v>
       </c>
@@ -1019,7 +1019,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="1" t="s">
         <v>59</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="1" t="s">
         <v>62</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="1" t="s">
         <v>68</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="3" t="s">
         <v>70</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="1" t="s">
         <v>76</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="1" t="s">
         <v>79</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="3" t="s">
         <v>83</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="1" t="s">
         <v>89</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="1" t="s">
         <v>91</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="3" t="s">
         <v>93</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="3" t="s">
         <v>98</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="1" t="s">
         <v>104</v>
       </c>
@@ -1295,7 +1295,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="1" t="s">
         <v>106</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>111</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="1" t="s">
         <v>106</v>
       </c>

--- a/src/generated_files/mappings.xlsx
+++ b/src/generated_files/mappings.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="126">
   <si>
     <t>FFMPEG Generic Tag Name</t>
   </si>
@@ -374,6 +374,24 @@
   </si>
   <si>
     <t>WM/Picture</t>
+  </si>
+  <si>
+    <t>originalyear</t>
+  </si>
+  <si>
+    <t>original year of recording</t>
+  </si>
+  <si>
+    <t>TORY</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:originalyear</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> WM/OriginalReleaseYear</t>
+  </si>
+  <si>
+    <t>for year if needed</t>
   </si>
 </sst>
 </file>
@@ -789,7 +807,7 @@
     <col min="7" max="7" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -812,7 +830,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -835,7 +853,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
@@ -858,7 +876,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
@@ -881,7 +899,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3" t="s">
         <v>26</v>
       </c>
@@ -904,7 +922,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3" t="s">
         <v>32</v>
       </c>
@@ -927,7 +945,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3" t="s">
         <v>38</v>
       </c>
@@ -950,7 +968,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1" t="s">
         <v>43</v>
       </c>
@@ -973,7 +991,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3" t="s">
         <v>48</v>
       </c>
@@ -996,7 +1014,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
         <v>53</v>
       </c>
@@ -1019,7 +1037,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="1" t="s">
         <v>59</v>
       </c>
@@ -1042,7 +1060,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="1" t="s">
         <v>62</v>
       </c>
@@ -1065,7 +1083,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="1" t="s">
         <v>68</v>
       </c>
@@ -1088,7 +1106,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3" t="s">
         <v>70</v>
       </c>
@@ -1365,13 +1383,27 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
+      <c r="A26" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="6"/>

--- a/src/generated_files/mappings.xlsx
+++ b/src/generated_files/mappings.xlsx
@@ -1,23 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\src\generated_files\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28B4259-CD02-4193-A0B3-2585E940ED06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="126">
-  <si>
-    <t>FFMPEG Generic Tag Name</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="127">
   <si>
     <t>Description</t>
   </si>
@@ -346,9 +349,6 @@
     <t>----:com.apple.iTunes:MEDIA</t>
   </si>
   <si>
-    <t>WM/Media | media_type</t>
-  </si>
-  <si>
     <t>maybe</t>
   </si>
   <si>
@@ -392,13 +392,21 @@
   </si>
   <si>
     <t>for year if needed</t>
+  </si>
+  <si>
+    <t>WM/Media</t>
+  </si>
+  <si>
+    <t>FFMPEG</t>
+  </si>
+  <si>
+    <t>ID3v2.3 datatype</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -429,7 +437,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00b050"/>
+        <fgColor rgb="FF00B050"/>
       </patternFill>
     </fill>
   </fills>
@@ -450,16 +458,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -467,41 +475,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -512,10 +517,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -553,71 +558,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -645,7 +650,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -668,11 +673,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -681,13 +686,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -697,7 +702,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -706,7 +711,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -715,7 +720,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -723,10 +728,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -791,637 +796,653 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="25.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="41.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="16.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="21.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="27.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="27.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" customWidth="1"/>
+    <col min="6" max="6" width="32" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="H3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3"/>
+      <c r="F5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="H5" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3"/>
+      <c r="F6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3"/>
+      <c r="F7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="1" t="s">
+      <c r="B8" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>45</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>45</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="3" t="s">
+      <c r="B9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="D11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="B12" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="1" t="s">
+    </row>
+    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="4" t="s">
+    </row>
+    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="B14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="1" t="s">
+    </row>
+    <row r="16" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="1" t="s">
+    </row>
+    <row r="17" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
-      <c r="A15" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="1" t="s">
+    </row>
+    <row r="19" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
-      <c r="A16" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E16" s="1" t="s">
+    </row>
+    <row r="20" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
-      <c r="A17" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
-      <c r="A18" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
-      <c r="A19" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
-      <c r="A20" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
-      <c r="A21" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
-      <c r="A22" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B22" s="4" t="s">
+    </row>
+    <row r="23" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
-      <c r="A23" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="1"/>
+      <c r="F23" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="G23" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F23" s="1" t="s">
+    </row>
+    <row r="24" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="C24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
-      <c r="A24" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B24" s="1" t="s">
+      <c r="E24" s="1"/>
+      <c r="F24" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="1" t="s">
+      <c r="G24" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="H24" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" t="s">
         <v>114</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="C25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="6" t="s">
+      <c r="E25" s="1"/>
+      <c r="F25" t="s">
         <v>116</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="1" t="s">
+      <c r="G25" t="s">
         <v>117</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="H25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>118</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="B26" t="s">
         <v>119</v>
       </c>
-      <c r="G25" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="6" t="s">
+      <c r="C26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" t="s">
         <v>120</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="F26" t="s">
         <v>121</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="6" t="s">
+      <c r="G26" t="s">
         <v>122</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="H26" t="s">
         <v>123</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
+    </row>
+    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="1"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
+    </row>
+    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="1"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/generated_files/mappings.xlsx
+++ b/src/generated_files/mappings.xlsx
@@ -1,26 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\src\generated_files\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28B4259-CD02-4193-A0B3-2585E940ED06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="133">
+  <si>
+    <t>FFMPEG</t>
+  </si>
   <si>
     <t>Description</t>
   </si>
@@ -31,6 +28,9 @@
     <t>ID3v2.3 (mp3)</t>
   </si>
   <si>
+    <t>ID3v2.3 datatype</t>
+  </si>
+  <si>
     <t>MP4 (m4a)</t>
   </si>
   <si>
@@ -91,7 +91,7 @@
     <t>TPE1</t>
   </si>
   <si>
-    <t xml:space="preserve"> ©art | ©ART</t>
+    <t xml:space="preserve"> ©art </t>
   </si>
   <si>
     <t>Author</t>
@@ -106,7 +106,7 @@
     <t>Comments</t>
   </si>
   <si>
-    <t>COMM:description</t>
+    <t>COMM::lng</t>
   </si>
   <si>
     <t xml:space="preserve"> ©cmt</t>
@@ -166,6 +166,9 @@
     <t>date</t>
   </si>
   <si>
+    <t>date when the work was created, preferably in ISO 8601</t>
+  </si>
+  <si>
     <t>Year</t>
   </si>
   <si>
@@ -217,7 +220,7 @@
     <t>TENC</t>
   </si>
   <si>
-    <t xml:space="preserve"> ©enc | ©too</t>
+    <t xml:space="preserve"> ©enc</t>
   </si>
   <si>
     <t>WM/EncodedBy</t>
@@ -241,7 +244,7 @@
     <t>TCON</t>
   </si>
   <si>
-    <t xml:space="preserve"> ©gen | gnre</t>
+    <t xml:space="preserve"> ©gen</t>
   </si>
   <si>
     <t>WM/Genre</t>
@@ -340,7 +343,7 @@
     <t>as found</t>
   </si>
   <si>
-    <t xml:space="preserve">source media of audio, as found, eg: MEDIA | media_type </t>
+    <t>source media of audio, as found, eg: MEDIA</t>
   </si>
   <si>
     <t>TMED</t>
@@ -349,7 +352,7 @@
     <t>----:com.apple.iTunes:MEDIA</t>
   </si>
   <si>
-    <t>maybe</t>
+    <t>WM/Media</t>
   </si>
   <si>
     <t xml:space="preserve">is a compilation, as found </t>
@@ -367,6 +370,9 @@
     <t>cover art</t>
   </si>
   <si>
+    <t>icon</t>
+  </si>
+  <si>
     <t>APIC</t>
   </si>
   <si>
@@ -376,10 +382,7 @@
     <t>WM/Picture</t>
   </si>
   <si>
-    <t>originalyear</t>
-  </si>
-  <si>
-    <t>original year of recording</t>
+    <t>original release year</t>
   </si>
   <si>
     <t>TORY</t>
@@ -391,22 +394,32 @@
     <t xml:space="preserve"> WM/OriginalReleaseYear</t>
   </si>
   <si>
-    <t>for year if needed</t>
-  </si>
-  <si>
-    <t>WM/Media</t>
-  </si>
-  <si>
-    <t>FFMPEG</t>
-  </si>
-  <si>
-    <t>ID3v2.3 datatype</t>
+    <t>alternate for date</t>
+  </si>
+  <si>
+    <t>Original Release Year</t>
+  </si>
+  <si>
+    <t>TDOR</t>
+  </si>
+  <si>
+    <t>release year &amp; date</t>
+  </si>
+  <si>
+    <t>TDRC</t>
+  </si>
+  <si>
+    <t>user defined original year of recording</t>
+  </si>
+  <si>
+    <t>TXXX+originalyear</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -437,7 +450,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor rgb="FF00b050"/>
       </patternFill>
     </fill>
   </fills>
@@ -458,16 +471,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </left>
       <right style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </right>
       <top style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -475,38 +488,44 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="10">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -517,10 +536,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -558,71 +577,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -650,7 +669,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -673,11 +692,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -686,13 +705,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -702,7 +721,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -711,7 +730,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -720,7 +739,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -728,10 +747,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -796,653 +815,720 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="66.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" customWidth="1"/>
-    <col min="6" max="6" width="32" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="8" width="15.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="66.57642857142856" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="9" width="16.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="17.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="17.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="8" width="32.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="8" width="27.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="23.862142857142857" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="H7" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H12" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="D13" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H18" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="D19" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H22" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="D23" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="B24" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" t="s">
-        <v>114</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E25" s="1"/>
-      <c r="F25" t="s">
-        <v>116</v>
-      </c>
-      <c r="G25" t="s">
-        <v>117</v>
-      </c>
-      <c r="H25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>118</v>
-      </c>
-      <c r="B26" t="s">
-        <v>119</v>
+      <c r="F25" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+      <c r="A26" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>122</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" t="s">
-        <v>120</v>
-      </c>
-      <c r="F26" t="s">
-        <v>121</v>
-      </c>
-      <c r="G26" t="s">
-        <v>122</v>
-      </c>
-      <c r="H26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="1"/>
-    </row>
-    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="1"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+      <c r="A27" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="17.25">
+      <c r="A28" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+      <c r="A29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>126</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/generated_files/mappings.xlsx
+++ b/src/generated_files/mappings.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="135">
   <si>
     <t>FFMPEG</t>
   </si>
@@ -340,31 +340,37 @@
     <t>the total bitrate of the bitrate variant that the current stream is part of</t>
   </si>
   <si>
+    <t>mediatype</t>
+  </si>
+  <si>
+    <t>source media of audio, as found, eg: MEDIA</t>
+  </si>
+  <si>
+    <t>TMED</t>
+  </si>
+  <si>
+    <t>----:com.apple.iTunes:MEDIA</t>
+  </si>
+  <si>
+    <t>WM/Media</t>
+  </si>
+  <si>
+    <t>compilation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is a compilation, as found </t>
+  </si>
+  <si>
+    <t>TCMP</t>
+  </si>
+  <si>
+    <t>cpil</t>
+  </si>
+  <si>
+    <t>WM/IsCompilation</t>
+  </si>
+  <si>
     <t>as found</t>
-  </si>
-  <si>
-    <t>source media of audio, as found, eg: MEDIA</t>
-  </si>
-  <si>
-    <t>TMED</t>
-  </si>
-  <si>
-    <t>----:com.apple.iTunes:MEDIA</t>
-  </si>
-  <si>
-    <t>WM/Media</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is a compilation, as found </t>
-  </si>
-  <si>
-    <t>TCMP</t>
-  </si>
-  <si>
-    <t>cpil</t>
-  </si>
-  <si>
-    <t>WM/IsCompilation</t>
   </si>
   <si>
     <t>cover art</t>
@@ -420,7 +426,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -438,6 +444,12 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -508,14 +520,14 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -823,13 +835,13 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="8" width="15.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="66.57642857142856" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="9" width="16.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="8" width="17.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="8" width="17.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="32.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="27.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="8" width="23.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="9" width="66.57642857142856" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="16.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="9" width="17.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="9" width="17.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="9" width="32.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="27.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="9" width="23.862142857142857" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -1218,7 +1230,7 @@
         <v>48</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="3" t="s">
         <v>85</v>
       </c>
@@ -1242,7 +1254,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="1" t="s">
         <v>91</v>
       </c>
@@ -1266,7 +1278,7 @@
         <v>48</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="1" t="s">
         <v>93</v>
       </c>
@@ -1290,7 +1302,7 @@
         <v>48</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="3" t="s">
         <v>95</v>
       </c>
@@ -1314,7 +1326,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="3" t="s">
         <v>100</v>
       </c>
@@ -1338,7 +1350,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="1" t="s">
         <v>106</v>
       </c>
@@ -1362,7 +1374,7 @@
         <v>48</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="1" t="s">
         <v>108</v>
       </c>
@@ -1386,90 +1398,90 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+        <v>128</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6" t="s">
@@ -1479,21 +1491,21 @@
         <v>47</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="17.25">
       <c r="A28" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>46</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="6" t="s">
@@ -1503,31 +1515,31 @@
         <v>47</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E29" s="6"/>
       <c r="F29" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/src/generated_files/mappings.xlsx
+++ b/src/generated_files/mappings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\src\generated_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6EF9C5-8C4B-4671-AE06-54530D756E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A680B4C7-313A-45C4-A711-60B692A1BB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -813,7 +813,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -917,9 +917,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1449,7 +1446,7 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="39" t="s">
         <v>205</v>
       </c>
       <c r="B9" s="28" t="s">
@@ -2695,7 +2692,7 @@
       <c r="I51" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="K51" s="39"/>
+      <c r="K51" s="2"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K51">

--- a/src/generated_files/mappings.xlsx
+++ b/src/generated_files/mappings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\src\generated_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DB00D2-4CED-4C8E-8AD6-21B6D878C0F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23ED773D-5C5A-4E85-977F-F049BD26EC7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-8232" yWindow="-13068" windowWidth="23256" windowHeight="12576" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="239">
   <si>
     <t>Windows Display</t>
   </si>
@@ -760,6 +760,15 @@
   </si>
   <si>
     <t>GRP1</t>
+  </si>
+  <si>
+    <t>https://github.com/sergiomb2/libmp4v2/wiki/iTunesMetadata</t>
+  </si>
+  <si>
+    <t>https://atomicparsley.sourceforge.net/mpeg-4files.html</t>
+  </si>
+  <si>
+    <t>https://docs.mp3tag.de/mapping-table/</t>
   </si>
 </sst>
 </file>
@@ -888,18 +897,9 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFC6C6C6"/>
-      </left>
       <right/>
       <top/>
       <bottom/>
@@ -920,134 +920,87 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1314,10 +1267,10 @@
     <col min="1" max="1" width="60.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="32.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="50.7109375" bestFit="1" customWidth="1"/>
@@ -1325,1432 +1278,1507 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="J1" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="2" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="D2" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="38" t="s">
+      <c r="G2" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="37" t="s">
+      <c r="H2" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="37" t="s">
+      <c r="I2" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="K2" s="5"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
     </row>
     <row r="3" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="23" t="s">
         <v>216</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="37" t="s">
+      <c r="G3" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="H3" s="37" t="s">
+      <c r="H3" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="37" t="s">
+      <c r="I3" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="J3" s="15"/>
+      <c r="K3" s="28" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="24" t="s">
         <v>194</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="37" t="s">
+      <c r="F4" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="37" t="s">
+      <c r="G4" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="H4" s="37" t="s">
+      <c r="H4" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="37" t="s">
+      <c r="I4" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="J4" s="15"/>
+      <c r="K4" s="7" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="E5" s="9" t="s">
+      <c r="C5" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K5" s="3" t="s">
+      <c r="F5" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J5" s="15"/>
+      <c r="K5" s="29" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="E6" s="33" t="s">
+      <c r="C6" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="F6" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="G6" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="H6" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="I6" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="K6" s="24" t="s">
+      <c r="F6" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J6" s="15"/>
+      <c r="K6" s="19" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="E7" s="9" t="s">
+      <c r="C7" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="F7" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="E8" s="11" t="s">
+      <c r="C8" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="J8" s="29"/>
-      <c r="K8" t="s">
+      <c r="J8" s="3"/>
+      <c r="K8" s="15" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="E9" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="F9" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="G9" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="H9" s="25" t="s">
+      <c r="F9" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="H9" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="I9" s="25" t="s">
+      <c r="I9" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="J9" s="29" t="s">
+      <c r="J9" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" s="15" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="29" t="s">
+      <c r="J10" s="3" t="s">
         <v>223</v>
       </c>
+      <c r="K10" s="15" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="11" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="7" t="s">
         <v>28</v>
       </c>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="12" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="E12" s="9" t="s">
+      <c r="C12" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>160</v>
+      <c r="F12" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H13" s="34" t="s">
+      <c r="H13" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="5" t="s">
         <v>155</v>
       </c>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
     </row>
     <row r="14" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A14" s="36" t="s">
+      <c r="A14" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="E14" s="36" t="s">
+      <c r="E14" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="F14" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="G14" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="H14" s="37" t="s">
+      <c r="H14" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="I14" s="37" t="s">
+      <c r="I14" s="24" t="s">
         <v>19</v>
       </c>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
     </row>
     <row r="15" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="G15" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="I15" s="7" t="s">
         <v>30</v>
       </c>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
     </row>
     <row r="16" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>160</v>
-      </c>
+      <c r="F16" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
     </row>
     <row r="17" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="E17" s="11" t="s">
+      <c r="C17" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="K17" s="5"/>
+      <c r="F17" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
     </row>
     <row r="18" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H18" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="I18" s="35" t="s">
+      <c r="I18" s="22" t="s">
         <v>50</v>
       </c>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
     </row>
     <row r="19" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H19" s="22" t="s">
+      <c r="H19" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="I19" s="10" t="s">
+      <c r="I19" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="J19" s="29" t="s">
+      <c r="J19" s="3" t="s">
         <v>230</v>
       </c>
+      <c r="K19" s="15"/>
     </row>
     <row r="20" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>160</v>
-      </c>
+      <c r="F20" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
     </row>
     <row r="21" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="37" t="s">
+      <c r="B21" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="37" t="s">
+      <c r="C21" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="D21" s="37" t="s">
+      <c r="D21" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="E21" s="36" t="s">
+      <c r="E21" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="37" t="s">
+      <c r="F21" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="G21" s="37" t="s">
+      <c r="G21" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="H21" s="37" t="s">
+      <c r="H21" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="I21" s="37" t="s">
+      <c r="I21" s="24" t="s">
         <v>55</v>
       </c>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
     </row>
     <row r="22" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="E22" s="11" t="s">
+      <c r="C22" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="G22" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H22" s="10" t="s">
+      <c r="H22" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="I22" s="10" t="s">
+      <c r="I22" s="5" t="s">
         <v>150</v>
       </c>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
     </row>
     <row r="23" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A23" s="39" t="s">
+      <c r="A23" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="B23" s="39" t="s">
+      <c r="B23" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="40" t="s">
-        <v>160</v>
-      </c>
-      <c r="D23" s="40" t="s">
+      <c r="C23" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="D23" s="27" t="s">
         <v>227</v>
       </c>
-      <c r="E23" s="40" t="s">
+      <c r="E23" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="F23" s="40" t="s">
+      <c r="F23" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="G23" s="40" t="s">
+      <c r="G23" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="H23" s="39" t="s">
+      <c r="H23" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="I23" s="39" t="s">
+      <c r="I23" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="J23" s="30" t="s">
+      <c r="J23" s="15" t="s">
         <v>229</v>
       </c>
+      <c r="K23" s="15"/>
     </row>
     <row r="24" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="E24" s="11" t="s">
+      <c r="C24" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="G24" s="10" t="s">
+      <c r="G24" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="H24" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="I24" s="10" t="s">
+      <c r="I24" s="5" t="s">
         <v>152</v>
       </c>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
     </row>
     <row r="25" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="H25" s="21" t="s">
+      <c r="H25" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="I25" s="21" t="s">
+      <c r="I25" s="16" t="s">
         <v>34</v>
       </c>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
     </row>
     <row r="26" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="F26" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="G26" s="10" t="s">
+      <c r="G26" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="H26" s="22" t="s">
+      <c r="H26" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="I26" s="22" t="s">
+      <c r="I26" s="17" t="s">
         <v>34</v>
       </c>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
     </row>
     <row r="27" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A27" s="19" t="s">
+      <c r="A27" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="E27" s="11" t="s">
+      <c r="C27" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E27" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="F27" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="H27" s="10" t="s">
+      <c r="F27" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H27" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="I27" s="10" t="s">
+      <c r="I27" s="5" t="s">
         <v>136</v>
       </c>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
     </row>
     <row r="28" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="F28" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>160</v>
-      </c>
+      <c r="F28" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
     </row>
     <row r="29" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="E29" s="9" t="s">
+      <c r="C29" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F29" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>160</v>
-      </c>
+      <c r="F29" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
     </row>
     <row r="30" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="H30" s="8" t="s">
+      <c r="C30" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="I30" s="21" t="s">
+      <c r="I30" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="K30" s="2"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="3"/>
     </row>
     <row r="31" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="E31" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="F31" s="10" t="s">
+      <c r="E31" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="G31" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="H31" s="34" t="s">
+      <c r="H31" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="I31" s="34" t="s">
+      <c r="I31" s="21" t="s">
         <v>158</v>
       </c>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
     </row>
     <row r="32" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="F32" s="8" t="s">
+      <c r="C32" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="G32" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="H32" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="I32" s="8" t="s">
+      <c r="I32" s="3" t="s">
         <v>78</v>
       </c>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
     </row>
     <row r="33" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="E33" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="F33" s="16" t="s">
+      <c r="E33" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="F33" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="G33" s="17" t="s">
+      <c r="G33" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="H33" s="16" t="s">
+      <c r="H33" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="I33" s="16" t="s">
+      <c r="I33" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="J33" t="s">
+      <c r="J33" s="15" t="s">
         <v>90</v>
       </c>
+      <c r="K33" s="15"/>
     </row>
     <row r="34" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="F34" s="16" t="s">
+      <c r="C34" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="F34" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="G34" s="16" t="s">
+      <c r="G34" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="H34" s="23" t="s">
+      <c r="H34" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="I34" s="23" t="s">
+      <c r="I34" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="J34" t="s">
+      <c r="J34" s="15" t="s">
         <v>90</v>
       </c>
+      <c r="K34" s="15"/>
     </row>
     <row r="35" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="E35" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="F35" s="16" t="s">
+      <c r="E35" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="F35" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="G35" s="16" t="s">
+      <c r="G35" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="H35" s="23" t="s">
+      <c r="H35" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="I35" s="23" t="s">
+      <c r="I35" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="J35" t="s">
+      <c r="J35" s="15" t="s">
         <v>90</v>
       </c>
+      <c r="K35" s="15"/>
     </row>
     <row r="36" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="F36" s="16" t="s">
+      <c r="C36" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="F36" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="G36" s="16" t="s">
+      <c r="G36" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="H36" s="16" t="s">
+      <c r="H36" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="I36" s="16" t="s">
+      <c r="I36" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="J36" t="s">
+      <c r="J36" s="15" t="s">
         <v>90</v>
       </c>
+      <c r="K36" s="15"/>
     </row>
     <row r="37" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="E37" s="9" t="s">
+      <c r="C37" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E37" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="F37" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>160</v>
-      </c>
+      <c r="F37" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J37" s="15"/>
+      <c r="K37" s="15"/>
     </row>
     <row r="38" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C38" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="E38" s="8" t="s">
+      <c r="C38" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="F38" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="H38" s="14" t="s">
+      <c r="F38" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H38" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="I38" s="14" t="s">
+      <c r="I38" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="J38" s="29" t="s">
+      <c r="J38" s="3" t="s">
         <v>231</v>
       </c>
+      <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A39" s="36" t="s">
+      <c r="A39" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="B39" s="37" t="s">
+      <c r="B39" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C39" s="37" t="s">
+      <c r="C39" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="D39" s="37" t="s">
+      <c r="D39" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="E39" s="36" t="s">
+      <c r="E39" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="F39" s="37" t="s">
+      <c r="F39" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="G39" s="37" t="s">
+      <c r="G39" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="H39" s="37" t="s">
+      <c r="H39" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="I39" s="37" t="s">
+      <c r="I39" s="24" t="s">
         <v>128</v>
       </c>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
     </row>
     <row r="40" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A40" s="32" t="s">
+      <c r="A40" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B40" s="32" t="s">
+      <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="D40" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="E40" s="33" t="s">
+      <c r="C40" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E40" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="F40" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="G40" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="H40" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="I40" s="32" t="s">
-        <v>160</v>
-      </c>
+      <c r="F40" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
     </row>
     <row r="41" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A41" s="13" t="s">
+      <c r="A41" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="B41" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="E41" s="13" t="s">
+      <c r="E41" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F41" s="12" t="s">
+      <c r="F41" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G41" s="12" t="s">
+      <c r="G41" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="H41" s="12" t="s">
+      <c r="H41" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="I41" s="12" t="s">
+      <c r="I41" s="7" t="s">
         <v>64</v>
       </c>
+      <c r="J41" s="15"/>
+      <c r="K41" s="15"/>
     </row>
     <row r="42" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A42" s="32" t="s">
+      <c r="A42" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B42" s="32" t="s">
+      <c r="B42" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C42" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="D42" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="E42" s="33" t="s">
+      <c r="C42" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E42" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="F42" s="32" t="s">
+      <c r="F42" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="G42" s="32" t="s">
+      <c r="G42" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="H42" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="I42" s="32" t="s">
+      <c r="H42" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="J42" s="29" t="s">
+      <c r="J42" s="3" t="s">
         <v>232</v>
       </c>
+      <c r="K42" s="15"/>
     </row>
     <row r="43" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C43" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="E43" s="9" t="s">
+      <c r="C43" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E43" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F43" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="I43" s="8" t="s">
-        <v>160</v>
-      </c>
+      <c r="F43" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J43" s="15"/>
+      <c r="K43" s="15"/>
     </row>
     <row r="44" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C44" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="E44" s="11" t="s">
+      <c r="E44" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="F44" s="10" t="s">
+      <c r="F44" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="G44" s="10" t="s">
+      <c r="G44" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H44" s="22" t="s">
+      <c r="H44" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="I44" s="22" t="s">
+      <c r="I44" s="17" t="s">
         <v>34</v>
       </c>
+      <c r="J44" s="15"/>
+      <c r="K44" s="15"/>
     </row>
     <row r="45" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C45" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="E45" s="11" t="s">
+      <c r="C45" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E45" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="F45" s="10" t="s">
+      <c r="F45" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G45" s="10" t="s">
+      <c r="G45" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H45" s="10" t="s">
+      <c r="H45" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="I45" s="10" t="s">
+      <c r="I45" s="5" t="s">
         <v>145</v>
       </c>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15"/>
     </row>
     <row r="46" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A46" s="36" t="s">
+      <c r="A46" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="B46" s="37" t="s">
+      <c r="B46" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C46" s="37" t="s">
+      <c r="C46" s="24" t="s">
         <v>214</v>
       </c>
-      <c r="D46" s="37" t="s">
+      <c r="D46" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="E46" s="36" t="s">
+      <c r="E46" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="F46" s="37" t="s">
+      <c r="F46" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="G46" s="37" t="s">
+      <c r="G46" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="H46" s="37" t="s">
+      <c r="H46" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="I46" s="37" t="s">
+      <c r="I46" s="24" t="s">
         <v>66</v>
       </c>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15"/>
     </row>
     <row r="47" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A47" s="36" t="s">
+      <c r="A47" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B47" s="37" t="s">
+      <c r="B47" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C47" s="37" t="s">
+      <c r="C47" s="24" t="s">
         <v>215</v>
       </c>
-      <c r="D47" s="37" t="s">
+      <c r="D47" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="E47" s="36" t="s">
+      <c r="E47" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="F47" s="37" t="s">
+      <c r="F47" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="G47" s="37" t="s">
+      <c r="G47" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="H47" s="37" t="s">
+      <c r="H47" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="I47" s="37" t="s">
+      <c r="I47" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="J47" s="29" t="s">
+      <c r="J47" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="K47" s="2"/>
+      <c r="K47" s="3"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D2:K47">
